--- a/example/constants.xlsx
+++ b/example/constants.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rdalke\Projects\MSE_Python\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18799047-088E-4CA5-BC0E-3E7F397A6B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{331A100E-0893-4EBA-9A3D-7EF16EC4D231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{695A8AAC-3E41-4CE5-BF4B-C22C8653E5B5}"/>
   </bookViews>
